--- a/Simulations_and_Calc/Driverboard/Driverboard.xlsx
+++ b/Simulations_and_Calc/Driverboard/Driverboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FHTW_Daniel_Stevic\Masterarbeit\Dimensionierung_und_Simulation\Driverboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10973B6-3934-4FDA-BE87-7525BAA2A890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E124AB3-5A22-4294-BB35-FB3D4B100726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,9 +112,6 @@
   </si>
   <si>
     <t>Po_bias[mW]</t>
-  </si>
-  <si>
-    <t>PT</t>
   </si>
   <si>
     <t>with datasheet</t>
@@ -168,6 +165,9 @@
       </rPr>
       <t xml:space="preserve"> [A]</t>
     </r>
+  </si>
+  <si>
+    <t>PT [mW]</t>
   </si>
 </sst>
 </file>
@@ -668,7 +668,7 @@
     </row>
     <row r="3" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>0</v>
@@ -680,16 +680,16 @@
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>4</v>
@@ -806,12 +806,12 @@
         <v>15</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="1">
         <f>D14+E14</f>
@@ -835,12 +835,12 @@
         <v>100</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.25">
@@ -851,7 +851,7 @@
     </row>
     <row r="39" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J39" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
